--- a/Config/Excel/GameConfig/SkillTargetingConfig.xlsx
+++ b/Config/Excel/GameConfig/SkillTargetingConfig.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1">
@@ -1079,25 +1079,30 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>SearchRadius</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>SectorAngle</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>TargetCampRelation</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>RequireAlive</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>SortRule</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
@@ -1146,20 +1151,25 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1203,25 +1213,30 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>搜索半径</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>扇形角度</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>目标阵营关系</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>是否要求目标存活</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>排序规则</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
@@ -1232,16 +1247,16 @@
         <v>31001</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -1250,17 +1265,20 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>玩家单体近战普攻</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>玩家近战横扫普攻，可同时命中3个近距离目标</t>
         </is>
       </c>
     </row>
@@ -1287,15 +1305,18 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>普通怪物单体近战普攻</t>
         </is>
@@ -1324,15 +1345,18 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>精英怪物单体近战普攻</t>
         </is>
@@ -1361,15 +1385,18 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Boss单体近战普攻</t>
         </is>

--- a/Config/Excel/GameConfig/SkillTargetingConfig.xlsx
+++ b/Config/Excel/GameConfig/SkillTargetingConfig.xlsx
@@ -1,184 +1,305 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="15320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowHeight="15320"/>
   </bookViews>
   <sheets>
-    <sheet name="SkillTargetingConfig" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SkillTargetingConfig" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>SelectType</t>
+  </si>
+  <si>
+    <t>MaxTargetCount</t>
+  </si>
+  <si>
+    <t>CastRange</t>
+  </si>
+  <si>
+    <t>EdgeDistance</t>
+  </si>
+  <si>
+    <t>UseCollisionRadius</t>
+  </si>
+  <si>
+    <t>SearchRadius</t>
+  </si>
+  <si>
+    <t>SectorAngle</t>
+  </si>
+  <si>
+    <t>TargetCampRelation</t>
+  </si>
+  <si>
+    <t>RequireAlive</t>
+  </si>
+  <si>
+    <t>SortRule</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>主键</t>
+  </si>
+  <si>
+    <t>选目标方式</t>
+  </si>
+  <si>
+    <t>最大目标数量</t>
+  </si>
+  <si>
+    <t>基础施法距离</t>
+  </si>
+  <si>
+    <t>边缘补偿距离</t>
+  </si>
+  <si>
+    <t>是否使用碰撞半径</t>
+  </si>
+  <si>
+    <t>搜索半径</t>
+  </si>
+  <si>
+    <t>扇形角度</t>
+  </si>
+  <si>
+    <t>目标阵营关系</t>
+  </si>
+  <si>
+    <t>是否要求目标存活</t>
+  </si>
+  <si>
+    <t>排序规则</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>玩家近战横扫普攻，可同时命中3个近距离目标</t>
+  </si>
+  <si>
+    <t>普通怪物单体近战普攻</t>
+  </si>
+  <si>
+    <t>精英怪物单体近战普攻</t>
+  </si>
+  <si>
+    <t>Boss单体近战普攻</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="21">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -478,154 +599,154 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -679,74 +800,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1033,376 +1091,288 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>SelectType</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>MaxTargetCount</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>CastRange</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>EdgeDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>UseCollisionRadius</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>SearchRadius</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SectorAngle</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>TargetCampRelation</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>RequireAlive</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>SortRule</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Desc</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>选目标方式</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>最大目标数量</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>基础施法距离</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>边缘补偿距离</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>是否使用碰撞半径</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>搜索半径</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>扇形角度</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>目标阵营关系</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>是否要求目标存活</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>排序规则</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="n">
+    <row r="4" spans="1:13">
+      <c r="B4">
         <v>31001</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
         <v>0.45</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>1</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>2</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>玩家近战横扫普攻，可同时命中3个近距离目标</t>
-        </is>
+      <c r="M4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="n">
+    <row r="5" spans="1:13">
+      <c r="B5">
         <v>31002</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>2</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>0.15</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>1</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>2</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>普通怪物单体近战普攻</t>
-        </is>
+      <c r="M5" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="n">
+    <row r="6" spans="1:13">
+      <c r="B6">
         <v>31003</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>2</v>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>0.2</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>2</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>精英怪物单体近战普攻</t>
-        </is>
+      <c r="M6" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" t="n">
+    <row r="7" spans="1:13">
+      <c r="B7">
         <v>31004</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <v>0.3</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>1</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>2</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Boss单体近战普攻</t>
-        </is>
+      <c r="M7" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/Excel/GameConfig/SkillTargetingConfig.xlsx
+++ b/Config/Excel/GameConfig/SkillTargetingConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15320"/>
+    <workbookView windowWidth="24940" windowHeight="15320"/>
   </bookViews>
   <sheets>
     <sheet name="SkillTargetingConfig" sheetId="1" r:id="rId1"/>
@@ -1095,6 +1095,11 @@
   <sheetPr/>
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <cols>
+    <col min="5" max="5" width="19.3942307692308" customWidth="1"/>
+    <col min="8" max="8" width="26.9134615384615" customWidth="1"/>
+    <col min="9" max="9" width="21.6346153846154" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
@@ -1230,7 +1235,7 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>0.45</v>
